--- a/Result/profitability/3049.xlsx
+++ b/Result/profitability/3049.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.68</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.04375</v>
       </c>
       <c r="N2" t="n">
-        <v>-13.97499999999999</v>
+        <v>-2.718749999999993</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1075</v>
+        <v>0.19875</v>
       </c>
       <c r="N3" t="n">
-        <v>-4.493749999999992</v>
+        <v>3.506250000000008</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.08</v>
       </c>
       <c r="M4" t="n">
-        <v>0.14125</v>
+        <v>0.23875</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.483749999999992</v>
+        <v>9.331250000000006</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.39</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.002499999999999974</v>
+        <v>0.09375000000000003</v>
       </c>
       <c r="N5" t="n">
-        <v>-6.034999999999991</v>
+        <v>4.591250000000008</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-1.26</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.13125</v>
+        <v>-0.03999999999999997</v>
       </c>
       <c r="N6" t="n">
-        <v>-15.30499999999999</v>
+        <v>-4.103749999999993</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,16 +1264,16 @@
         <v>-0.4</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1575</v>
+        <v>-0.09249999999999997</v>
       </c>
       <c r="N7" t="n">
-        <v>-11.20874999999999</v>
+        <v>-3.433749999999993</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.19625</v>
+        <v>-0.12375</v>
       </c>
       <c r="N8" t="n">
-        <v>-9.77249999999999</v>
+        <v>-8.511249999999992</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3049</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>99</v>
+      </c>
+      <c r="D75" t="n">
+        <v>50</v>
+      </c>
+      <c r="E75" t="n">
+        <v>49</v>
+      </c>
+      <c r="F75" t="n">
+        <v>49.69</v>
+      </c>
+      <c r="G75" t="n">
+        <v>7</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.38%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>527</v>
+      </c>
+      <c r="J75" t="n">
+        <v>535</v>
+      </c>
+      <c r="K75" t="n">
+        <v>435</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.08750000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-11.24499999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.5800000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2547979797979798</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.347826086956522</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-2.406851642129105</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
